--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>보고서</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>실패</v>
+        <v>코드 포인트</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>개 검사</v>
+        <v>게인 곡선</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>{lib} 기반</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>구독</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>닫기</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>이메일 주소</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(선택)</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>취소</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>개인정보 처리방침</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>오류:</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>XML로 변환</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>JSON으로 변환</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>ICC로 변환</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>XML로 변환 중…</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>프로파일 ID</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>태그 이름</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>오프셋</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>크기</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>패딩</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>유형</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} 배열</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(내용 없음)</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>바이트</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>검증 출력 없음</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>심각한 검증 오류</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>유효</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>경고</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>오류</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>알 수 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>통과</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>실패</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>검증 세부 정보</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>트리거 항목</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>항목</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>현재 값</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>필수: 0</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>예상: {value}</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>잘못됨</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>닫기</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>들여쓰기</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>키 정렬</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>색 원색</v>
+        <v>환경</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>전달 특성</v>
+        <v>감지 중…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>행렬 계수</v>
+        <v>환경을 감지할 수 없습니다.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>풀 레인지</v>
+        <v>광색역</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>내로 레인지</v>
+        <v>HDR 캔버스 경로</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>예</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>보고서</v>
+        <v>아니오</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>실패</v>
+        <v>보고되지 않음</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>개 검사</v>
+        <v>형식</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>검사</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>{lib} 기반</v>
+        <v>포함된 ICC 프로파일 읽기 — 코덱 불필요</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>구독</v>
+        <v>픽셀 표시</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>흰색보다 밝게 렌더링</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>닫기</v>
+        <v>브라우저는 디스플레이의 HDR 헤드룸 양을 보고할 수 없고 HDR 경로 존재 여부만 알 수 있습니다.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>이메일 주소</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>you@example.com</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(선택)</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>취소</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>구독</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>닫기</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>개인정보 처리방침</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>오류:</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>XML로 변환</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>ICC로 변환</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>XML로 변환 중…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>프로파일 ID</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>태그 이름</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>오프셋</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>크기</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>패딩</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>유형</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>{type} 배열</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(내용 없음)</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>바이트</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>검증 출력 없음</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>유효</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>경고</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>오류</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>알 수 없음</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>통과</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>실패</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>검증 세부 정보</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>트리거 항목</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>항목</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>현재 값</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>필수: 0</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>예상: {value}</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>잘못됨</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>닫기</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>들여쓰기</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>키 정렬</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>감지 중…</v>
+        <v>SDR 폴백을 표시 중</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>환경을 감지할 수 없습니다.</v>
+        <v>체인에 HDR 프로파일 포함</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR 디스플레이</v>
+        <v>HDR 프로파일을 통한 변환은 해당 AToB0Tag(8.10.6이 요구하는 고정 SDR 렌더링)를 사용합니다. 8.10.1이 TRC 태그를 허용하지 않기 때문입니다. 결과는 그 폴백이며 HDR 동작이 아닙니다.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>광색역</v>
+        <v>이들은 TRC 태그가 없는 HDR 프로파일이므로 색영역은 AToB0Tag에서 구성됩니다. 이는 HDR 처리를 하지 않는 소비자를 위해 8.10.6 조항이 요구하는 고정된 SDR 렌더링입니다. 프로파일의 HDR 색영역이 아니며, 그것은 제한된 PCS에 그릴 수 없습니다.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>HDR 캔버스 경로</v>
+        <v>감지 중…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>환경을 감지할 수 없습니다.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>없음</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>예</v>
+        <v>광색역</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>아니오</v>
+        <v>HDR 캔버스 경로</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>보고되지 않음</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>형식</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>검사</v>
+        <v>예</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>표시</v>
+        <v>아니오</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>보고되지 않음</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>포함된 ICC 프로파일 읽기 — 코덱 불필요</v>
+        <v>형식</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>픽셀 표시</v>
+        <v>검사</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>흰색보다 밝게 렌더링</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>profiletool이 직접 디코딩하므로 브라우저와 무관</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>브라우저는 디스플레이의 HDR 헤드룸 양을 보고할 수 없고 HDR 경로 존재 여부만 알 수 있습니다.</v>
+        <v>포함된 ICC 프로파일 읽기 — 코덱 불필요</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>색 원색</v>
+        <v>픽셀 표시</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>전달 특성</v>
+        <v>흰색보다 밝게 렌더링</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>행렬 계수</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>브라우저는 디스플레이의 HDR 헤드룸 양을 보고할 수 없고 HDR 경로 존재 여부만 알 수 있습니다.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>풀 레인지</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>내로 레인지</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>보고서</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>실패</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>개 검사</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>{lib} 기반</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>구독</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>닫기</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>you@example.com</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(선택)</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>취소</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>구독</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>닫기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>개인정보 처리방침</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>오류:</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>XML로 변환</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>JSON으로 변환</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>ICC로 변환</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>XML로 변환 중…</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>프로파일 ID</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>태그 이름</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>오프셋</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>크기</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>패딩</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>유형</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>{type} 배열</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(내용 없음)</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>바이트</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>검증 출력 없음</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>심각한 검증 오류</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>유효</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>경고</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>오류</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>알 수 없음</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>통과</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>실패</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>트리거 항목</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>항목</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>현재 값</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>필수: 0</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>예상: {value}</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>잘못됨</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>닫기</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>들여쓰기</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>키 정렬</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>색 원색</v>
+        <v>브라우저 플래그</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>전달 특성</v>
+        <v>켜짐</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>행렬 계수</v>
+        <v>꺼짐</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>여기서는 감지할 수 없음</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>풀 레인지</v>
+        <v>이 브라우저에서 HDR 렌더링에 필요합니다. WebGPU가 없어 HDR 캔버스가 유일한 경로입니다. 프로파일 검사는 이것 없이도 작동합니다.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>내로 레인지</v>
+        <v>선택 사항: HDR은 WebGPU로 렌더링할 수 있지만, 켜면 HDR 캔버스 경로가 추가되고 profiletool이 화면의 실제 HDR 헤드룸을 읽을 수 있습니다.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>웹 페이지는 플래그 페이지를 열 수 없습니다. 이 주소를 주소창에 붙여넣고 Enabled로 설정한 뒤 브라우저를 다시 시작하세요.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>복사</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>복사됨</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>보고서</v>
+        <v>복사 실패 — 주소를 선택해 복사하세요.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>실패</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>개 검사</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>{lib} 기반</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>구독</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>닫기</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>이메일 주소</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>you@example.com</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(선택)</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>취소</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>구독</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>닫기</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>개인정보 처리방침</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>오류:</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>XML로 변환</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>JSON으로 변환</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC로 변환</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>XML로 변환 중…</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>프로파일 ID</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>태그 이름</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>오프셋</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>크기</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>패딩</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>유형</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>{type} 배열</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(내용 없음)</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>바이트</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>검증 출력 없음</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>심각한 검증 오류</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>유효</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>경고</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>오류</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>알 수 없음</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>통과</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>실패</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>트리거 항목</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>항목</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>현재 값</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>필수: 0</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>예상: {value}</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>잘못됨</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>닫기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>들여쓰기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>키 정렬</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>브라우저는 디스플레이의 HDR 헤드룸 양을 보고할 수 없고 HDR 경로 존재 여부만 알 수 있습니다.</v>
+        <v>이 브라우저는 디스플레이의 HDR 헤드룸을 보고하지 않았고 HDR 경로 존재 여부만 알 수 있습니다.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>색 원색</v>
+        <v>픽셀 비율</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>전달 특성</v>
+        <v>현재 모니터</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>행렬 계수</v>
+        <v>이름 없음</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>기본</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>풀 레인지</v>
+        <v>내장</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>내로 레인지</v>
+        <v>HDR 헤드룸</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>이 브라우저에서 제공하지 않음</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>브라우저가 보고한 값 그대로 표시합니다. 단위는 아직 표준화되지 않았으며, SDR 화면에서 0이 보고되었습니다.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>보고서</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>실패</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>개 검사</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>{lib} 기반</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>구독</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>닫기</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>이메일 주소</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>you@example.com</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(선택)</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>취소</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>구독</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>닫기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>개인정보 처리방침</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>오류:</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>XML로 변환</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>ICC로 변환</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>XML로 변환 중…</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>프로파일 ID</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>태그 이름</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>오프셋</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>크기</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>패딩</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>유형</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>{type} 배열</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(내용 없음)</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>바이트</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>검증 출력 없음</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>심각한 검증 오류</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>유효</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>경고</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>오류</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>알 수 없음</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>통과</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>실패</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>검증 세부 정보</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>트리거 항목</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>항목</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>현재 값</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>필수: 0</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>예상: {value}</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>잘못됨</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>닫기</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>들여쓰기</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>키 정렬</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>브라우저가 보고한 값 그대로 표시합니다. 단위는 아직 표준화되지 않았으며, SDR 화면에서 0이 보고되었습니다.</v>
+        <v>Chromium은 이를 스톱 단위로 보고합니다: 디스플레이 최대 밝기 ÷ SDR 흰색 레벨의 log₂. Windows에서는 Chrome이 디스플레이를 다시 읽을 때(창을 다른 화면으로 옮기거나 Chrome을 다시 활성화할 때)만 갱신되며, 밝기를 바꿔도 갱신되지 않습니다.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{stops} 스톱 (≈ SDR 흰색의 {ratio}배)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>디스플레이 식별</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>색 원색</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>전달 특성</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>행렬 계수</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>풀 레인지</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>내로 레인지</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>보고서</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>디스플레이 식별</v>
+        <v>디스플레이 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>이 디스플레이에서 HDR 이미지 한 장을 봅니다. 브라우저가 디코딩할 수 있는 파일은 브라우저가 직접 표시하고, OpenEXR은 profiletool이 디코딩해 렌더링합니다.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>HDR 이미지를 여기에 놓거나 클릭해 선택하세요</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>OpenEXR, AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC도.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>다른 이미지 선택</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>내장 ICC 프로파일</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>없음 — OpenEXR은 색도 좌표로 색을 나타냅니다</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>색 원색</v>
+        <v>확인 중…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>전달 특성</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>행렬 계수</v>
+        <v>프로파일 탭에서 열기</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>게인 맵</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>풀 레인지</v>
+        <v>감지됨, 디코딩 안 함</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>내로 레인지</v>
+        <v>이미지가 아닙니다. 프로파일은 프로파일 패널에서 불러오세요.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>profiletool이 인식하지 못하는 이미지 형식입니다.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>TIFF 픽셀은 아직 여기에 표시되지 않습니다. 브라우저는 TIFF를 디코딩하지 않으며, 16비트 TIFF에서 HDR을 인코딩하는 방식도 아직 정해지지 않았습니다(4.3단계). 내장 프로파일은 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>이 이미지는 여기서 표시할 수 없습니다:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>보고서</v>
+        <v>내장 프로파일은 여전히 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>실패</v>
+        <v>표시 주체</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>개 검사</v>
+        <v>브라우저</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>브라우저는 내장 ICC 프로파일로만 표시된 HDR을 무시하므로 이 이미지는 어둡고 밋밋해 보일 수 있습니다.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>{lib} 기반</v>
+        <v>이 브라우저는 이미지를 SDR과 HDR 사이에서 전환할 수 없으므로 브라우저가 렌더링한 그대로 표시합니다.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>구독</v>
+        <v>브라우저가 이 이미지를 디코딩하지 못했습니다.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>HDR 캔버스(float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>닫기</v>
+        <v>WebGPU(확장 범위)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>SDR 캔버스(톤 매핑)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>이메일 주소</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>you@example.com</v>
+        <v>가장 밝은 픽셀</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>SDR 흰색의 {n}배</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(선택)</v>
+        <v>색도 좌표</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>명시 안 됨 — Rec. 709로 가정</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>{from}을(를) 여기서 사용할 수 없습니다({why}). 다음 출력을 사용합니다.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>취소</v>
+        <v>이 출력은 흰색보다 밝은 값을 담을 수 없어 톤 매핑된 SDR 렌더링을 표시합니다.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>구독</v>
+        <v>노출</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>{n} 스톱</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>디코딩할 수 없음:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>닫기</v>
+        <v>디코딩 중…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>개인정보 처리방침</v>
+        <v>다이내믹 레인지</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>오류:</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>XML로 변환</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>JSON으로 변환</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>ICC로 변환</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>XML로 변환 중…</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>프로파일 ID</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>태그 이름</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>오프셋</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>크기</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>패딩</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>유형</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>{type} 배열</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(내용 없음)</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>바이트</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>검증 출력 없음</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>심각한 검증 오류</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>유효</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>경고</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>오류</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>알 수 없음</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>통과</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>실패</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>검증 세부 정보</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>트리거 항목</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>항목</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>현재 값</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>필수: 0</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>예상: {value}</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>잘못됨</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>닫기</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>들여쓰기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>키 정렬</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>개인정보 처리방침</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>유효한 이메일 주소를 입력하세요.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>양식을 확인하고 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>오류:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>XML로 변환</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>JSON으로 변환</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>ICC로 변환</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>XML로 변환 중…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>JSON으로 변환 중…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>ICC로 변환 중…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>ICC 프로파일 로드</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>ICC 프로파일 파일용 드롭 영역</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>프로파일 ID</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>태그를 찾을 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>태그 이름</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>이 브라우저는 디코딩합니다</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>이 브라우저는 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>기준선</v>
+        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>이후 릴리스로 연기됨</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>알 수 없는 형식</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>{os}의 {browser}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{name} · HDR 디스플레이 감지됨</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>{name} · SDR 디스플레이</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>변경 없음</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>디스플레이 식별</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>색 원색</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>전달 특성</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>행렬 계수</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>풀 레인지</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>내로 레인지</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>보고서</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>실패</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>개 검사</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>{lib} 기반</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>구독</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>닫기</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>이메일 주소</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>you@example.com</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(선택)</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>취소</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>구독</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>닫기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>개인정보 처리방침</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>오류:</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>XML로 변환</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>ICC로 변환</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>XML로 변환 중…</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>프로파일 ID</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>태그 이름</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>오프셋</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>크기</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>패딩</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>유형</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>{type} 배열</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(내용 없음)</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>바이트</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>검증 출력 없음</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>심각한 검증 오류</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>유효</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>경고</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>오류</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>알 수 없음</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>통과</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>실패</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>검증 세부 정보</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>트리거 항목</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>항목</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>현재 값</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>필수: 0</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>예상: {value}</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>잘못됨</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>닫기</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>들여쓰기</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>키 정렬</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>디스플레이 최대치</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>1× — SDR 디스플레이</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>기준선</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>디스플레이에 맞춤</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>제한 없음</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>제한 {n} 스톱 ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>SDR 흰색</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>변경 없음</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>디스플레이 식별</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>색 원색</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>전달 특성</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>행렬 계수</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>풀 레인지</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>내로 레인지</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>보고서</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>실패</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>개 검사</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>{lib} 기반</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>구독</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>닫기</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>이메일 주소</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>you@example.com</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(선택)</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>취소</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>오류:</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>XML로 변환</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>JSON으로 변환</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>ICC로 변환</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>XML로 변환 중…</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>프로파일 ID</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>태그 이름</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>오프셋</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>크기</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>패딩</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>유형</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>{type} 배열</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(내용 없음)</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>바이트</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>검증 출력 없음</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>심각한 검증 오류</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>유효</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>경고</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>오류</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>알 수 없음</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>통과</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>실패</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>검증 세부 정보</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>트리거 항목</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>항목</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>현재 값</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>필수: 0</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>예상: {value}</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>잘못됨</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>닫기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>들여쓰기</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>키 정렬</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>SDR 흰색 패치</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>기준선</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>변경 없음</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>디스플레이 식별</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>색 원색</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>전달 특성</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>행렬 계수</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>풀 레인지</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>내로 레인지</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>보고서</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>실패</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>개 검사</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>구독</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>닫기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>이메일 주소</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>you@example.com</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(선택)</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>취소</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>구독</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>닫기</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>개인정보 처리방침</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>오류:</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>XML로 변환</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>JSON으로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>ICC로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>XML로 변환 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>태그 이름</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>오프셋</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>크기</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>패딩</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>유형</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>{type} 배열</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(내용 없음)</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>바이트</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>검증 출력 없음</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>유효</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>경고</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>오류</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>알 수 없음</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>통과</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>실패</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>검증 세부 정보</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>트리거 항목</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>현재 값</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>필수: 0</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>예상: {value}</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>잘못됨</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>닫기</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>키 정렬</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>프로파일 지정</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>없음 — 파일이 나타내는 대로</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>내장 프로파일 ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>기준선</v>
+        <v>풀의 HDR 프로파일</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>내장 프로파일</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>색상 엔진 경로</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>HDR 경로, 게인 곡선 적용</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>HDR 경로, 게인 곡선 없음</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>전달 함수</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>HDR 기준 흰색</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>변경 없음</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>OpenEXR은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>디스플레이 식별</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>색 원색</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>전달 특성</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>행렬 계수</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>풀 레인지</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>내로 레인지</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>보고서</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>실패</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>개 검사</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>{lib} 기반</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>구독</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>닫기</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>이메일 주소</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>you@example.com</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(선택)</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>취소</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>구독</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>닫기</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>개인정보 처리방침</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>오류:</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>XML로 변환</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>ICC로 변환</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>XML로 변환 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>프로파일 ID</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>태그 이름</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>오프셋</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>크기</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>패딩</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>유형</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>{type} 배열</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(내용 없음)</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>바이트</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>검증 출력 없음</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>심각한 검증 오류</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>유효</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>경고</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>오류</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>알 수 없음</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>통과</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>실패</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>검증 세부 정보</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>트리거 항목</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>항목</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>현재 값</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>필수: 0</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>예상: {value}</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>잘못됨</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>닫기</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>들여쓰기</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>키 정렬</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>기준선</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>OpenEXR은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>변경 없음</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>디스플레이 식별</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>색 원색</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>전달 특성</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>행렬 계수</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>풀 레인지</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>내로 레인지</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>보고서</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>실패</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>개 검사</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>{lib} 기반</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>구독</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>닫기</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>이메일 주소</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>you@example.com</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(선택)</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>취소</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>구독</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>닫기</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>개인정보 처리방침</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>오류:</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>XML로 변환</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>JSON으로 변환</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>ICC로 변환</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>XML로 변환 중…</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>프로파일 ID</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>태그 이름</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>오프셋</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>크기</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>패딩</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>유형</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>{type} 배열</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(내용 없음)</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>바이트</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>검증 출력 없음</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>심각한 검증 오류</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>유효</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>경고</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>오류</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>알 수 없음</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>통과</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>실패</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>검증 세부 정보</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>트리거 항목</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>항목</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>현재 값</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>필수: 0</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>예상: {value}</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>잘못됨</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>닫기</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>들여쓰기</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>키 정렬</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>이 디스플레이에서 HDR 이미지 한 장을 봅니다. 브라우저가 디코딩할 수 있는 파일은 브라우저가 직접 표시하고, OpenEXR은 profiletool이 디코딩해 렌더링합니다.</v>
+        <v>이 디스플레이에서 HDR 이미지 한 장을 봅니다. 브라우저가 디코딩할 수 있는 파일은 브라우저가 직접 표시하고, OpenEXR과 Radiance HDR은 profiletool이 디코딩해 렌더링합니다.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC도.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC도.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>확인 중…</v>
+        <v>없음 — Radiance HDR은 PRIMARIES 헤더로 색을 나타냅니다</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>없음</v>
+        <v>확인 중…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>프로파일 탭에서 열기</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>게인 맵</v>
+        <v>프로파일 탭에서 열기</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>감지됨, 디코딩 안 함</v>
+        <v>게인 맵</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>이미지가 아닙니다. 프로파일은 프로파일 패널에서 불러오세요.</v>
+        <v>감지됨, 디코딩 안 함</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>profiletool이 인식하지 못하는 이미지 형식입니다.</v>
+        <v>이미지가 아닙니다. 프로파일은 프로파일 패널에서 불러오세요.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>TIFF 픽셀은 아직 여기에 표시되지 않습니다. 브라우저는 TIFF를 디코딩하지 않으며, 16비트 TIFF에서 HDR을 인코딩하는 방식도 아직 정해지지 않았습니다(4.3단계). 내장 프로파일은 검사할 수 있습니다.</v>
+        <v>profiletool이 인식하지 못하는 이미지 형식입니다.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>이 이미지는 여기서 표시할 수 없습니다:</v>
+        <v>TIFF 픽셀은 아직 여기에 표시되지 않습니다. 브라우저는 TIFF를 디코딩하지 않으며, 16비트 TIFF에서 HDR을 인코딩하는 방식도 아직 정해지지 않았습니다(4.3단계). 내장 프로파일은 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>내장 프로파일은 여전히 검사할 수 있습니다.</v>
+        <v>이 이미지는 여기서 표시할 수 없습니다:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>표시 주체</v>
+        <v>내장 프로파일은 여전히 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>브라우저</v>
+        <v>표시 주체</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>브라우저</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>HDR 디스플레이</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>브라우저는 내장 ICC 프로파일로만 표시된 HDR을 무시하므로 이 이미지는 어둡고 밋밋해 보일 수 있습니다.</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>이 브라우저는 이미지를 SDR과 HDR 사이에서 전환할 수 없으므로 브라우저가 렌더링한 그대로 표시합니다.</v>
+        <v>브라우저는 내장 ICC 프로파일로만 표시된 HDR을 무시하므로 이 이미지는 어둡고 밋밋해 보일 수 있습니다.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>브라우저가 이 이미지를 디코딩하지 못했습니다.</v>
+        <v>이 브라우저는 이미지를 SDR과 HDR 사이에서 전환할 수 없으므로 브라우저가 렌더링한 그대로 표시합니다.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>출력</v>
+        <v>브라우저가 이 이미지를 디코딩하지 못했습니다.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>HDR 캔버스(float16)</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU(확장 범위)</v>
+        <v>HDR 캔버스(float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>SDR 캔버스(톤 매핑)</v>
+        <v>WebGPU(확장 범위)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>크기</v>
+        <v>SDR 캔버스(톤 매핑)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>가장 밝은 픽셀</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>SDR 흰색의 {n}배</v>
+        <v>가장 밝은 픽셀</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>색도 좌표</v>
+        <v>SDR 흰색의 {n}배</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>명시 안 됨 — Rec. 709로 가정</v>
+        <v>색도 좌표</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from}을(를) 여기서 사용할 수 없습니다({why}). 다음 출력을 사용합니다.</v>
+        <v>명시 안 됨 — Rec. 709로 가정</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>이 출력은 흰색보다 밝은 값을 담을 수 없어 톤 매핑된 SDR 렌더링을 표시합니다.</v>
+        <v>{from}을(를) 여기서 사용할 수 없습니다({why}). 다음 출력을 사용합니다.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>노출</v>
+        <v>이 출력은 흰색보다 밝은 값을 담을 수 없어 톤 매핑된 SDR 렌더링을 표시합니다.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} 스톱</v>
+        <v>노출</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>디코딩할 수 없음:</v>
+        <v>{n} 스톱</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>디코딩 중…</v>
+        <v>디코딩할 수 없음:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>다이내믹 레인지</v>
+        <v>디코딩 중…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
+        <v>다이내믹 레인지</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
+        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>이 브라우저는 디코딩합니다</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>이 브라우저는 디코딩하지 않습니다</v>
+        <v>이 브라우저는 디코딩합니다</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
+        <v>이 브라우저는 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
+        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>이후 릴리스로 연기됨</v>
+        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
+        <v>이후 릴리스로 연기됨</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
+        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
+        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
+        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
+        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>알 수 없는 형식</v>
+        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{os}의 {browser}</v>
+        <v>알 수 없는 형식</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · HDR 디스플레이 감지됨</v>
+        <v>{os}의 {browser}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · SDR 디스플레이</v>
+        <v>{name} · HDR 디스플레이 감지됨</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
+        <v>{name} · SDR 디스플레이</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
+        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>디스플레이 최대치</v>
+        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
+        <v>디스플레이 최대치</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — SDR 디스플레이</v>
+        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>알 수 없음</v>
+        <v>1× — SDR 디스플레이</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>디스플레이에 맞춤</v>
+        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
+        <v>디스플레이에 맞춤</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>제한 없음</v>
+        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>제한 {n} 스톱 ({r}×)</v>
+        <v>제한 없음</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>SDR 흰색</v>
+        <v>제한 {n} 스톱 ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
+        <v>SDR 흰색</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>SDR 흰색 패치</v>
+        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
+        <v>SDR 흰색 패치</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>프로파일 지정</v>
+        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>없음 — 파일이 나타내는 대로</v>
+        <v>프로파일 지정</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>내장 프로파일 ({n} B)</v>
+        <v>없음 — 파일이 나타내는 대로</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>풀의 HDR 프로파일</v>
+        <v>내장 프로파일 ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>프로파일</v>
+        <v>풀의 HDR 프로파일</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>내장 프로파일</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>색상 엔진 경로</v>
+        <v>내장 프로파일</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR 경로, 게인 곡선 적용</v>
+        <v>색상 엔진 경로</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 경로, 게인 곡선 없음</v>
+        <v>HDR 경로, 게인 곡선 적용</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
+        <v>HDR 경로, 게인 곡선 없음</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>전달 함수</v>
+        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>HDR 기준 흰색</v>
+        <v>전달 함수</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>목표 헤드룸</v>
+        <v>HDR 기준 흰색</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>톤 매핑</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>게인 곡선 (HAGC)</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>미리 계산된 SDR 대체 (AToB0)</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>끄기 — 개정 이전 CMM과 동일</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>프로파일 적용 중…</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR 프로파일</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>선형 전달 함수</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>비선형 전달 함수 (PQ, HLG)</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>기준선</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>변경 없음</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>디스플레이 식별</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>색 원색</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>전달 특성</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>행렬 계수</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>풀 레인지</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>내로 레인지</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>보고서</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
+        <v>이미지 세부 정보</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>제한 없음</v>
+        <v>사용할 수 없음 — 브라우저가 이 이미지를 렌더링하므로 지정한 피크로 제한할 수 없습니다</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>제한 {n} 스톱 ({r}×)</v>
+        <v>사용할 수 없음 — 이 출력은 SDR 흰색보다 밝은 부분을 표시하지 못합니다</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>SDR 흰색</v>
+        <v>사용할 수 없음 — 이 디스플레이의 피크를 알 수 없습니다</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
+        <v>확대</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>SDR 흰색 패치</v>
+        <v>축소</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
+        <v>이미지 맞춤</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>프로파일 지정</v>
+        <v>실제 픽셀(1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>없음 — 파일이 나타내는 대로</v>
+        <v>드래그하여 이동 · Ctrl+휠로 확대/축소 · 더블클릭으로 초기화</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>내장 프로파일 ({n} B)</v>
+        <v>드래그하여 이미지 영역 크기 조정, 더블클릭하면 기본 크기로 돌아갑니다</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>풀의 HDR 프로파일</v>
+        <v>이미지 보기</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>프로파일</v>
+        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>내장 프로파일</v>
+        <v>제한 없음</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>색상 엔진 경로</v>
+        <v>제한 {n} 스톱 ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 경로, 게인 곡선 적용</v>
+        <v>SDR 흰색</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>HDR 경로, 게인 곡선 없음</v>
+        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
+        <v>SDR 흰색 패치</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>전달 함수</v>
+        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>HDR 기준 흰색</v>
+        <v>프로파일 지정</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>목표 헤드룸</v>
+        <v>없음 — 파일이 나타내는 대로</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
+        <v>내장 프로파일 ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>톤 매핑</v>
+        <v>풀의 HDR 프로파일</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>게인 곡선 (HAGC)</v>
+        <v>내장 프로파일</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>미리 계산된 SDR 대체 (AToB0)</v>
+        <v>색상 엔진 경로</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>끄기 — 개정 이전 CMM과 동일</v>
+        <v>HDR 경로, 게인 곡선 적용</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>프로파일 적용 중…</v>
+        <v>HDR 경로, 게인 곡선 없음</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
+        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
+        <v>전달 함수</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
+        <v>HDR 기준 흰색</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR 프로파일</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>선형 전달 함수</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>비선형 전달 함수 (PQ, HLG)</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>기준선</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>변경 없음</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>디스플레이 식별</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>색 원색</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>전달 특성</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>행렬 계수</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>풀 레인지</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>내로 레인지</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>보고서</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>실패</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>개 검사</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>{lib} 기반</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>구독</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>닫기</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>이메일 주소</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>you@example.com</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(선택)</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>취소</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>구독</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>닫기</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>개인정보 처리방침</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>오류:</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>XML로 변환</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>JSON으로 변환</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>ICC로 변환</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>XML로 변환 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>프로파일 ID</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>태그 이름</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>오프셋</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>크기</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>패딩</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>유형</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>{type} 배열</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(내용 없음)</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>바이트</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>검증 출력 없음</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>심각한 검증 오류</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>유효</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>경고</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>오류</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>알 수 없음</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>통과</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>실패</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>검증 세부 정보</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>트리거 항목</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>항목</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>현재 값</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>필수: 0</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>예상: {value}</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>잘못됨</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>닫기</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>들여쓰기</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>키 정렬</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>색상 엔진을 통한 미리보기</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>{h}스톱에 맞춘 톤 매핑</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>기준 흰색</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>디스플레이 피크</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>미리보기를 사용할 수 없음: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>모든 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>입력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>디스플레이 헤드룸(스톱)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>게인(스톱)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>태그의 곡선</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>변경 없음</v>
+        <v>슬라이더</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>입력 = 디스플레이 피크</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>헤드룸별 회색 톤 곡선</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>디스플레이 식별</v>
+        <v>출력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>{h}스톱</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>{h}스톱(기준선)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>{h}스톱(슬라이더)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>색 원색</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>전달 특성</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>행렬 계수</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>풀 레인지</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>내로 레인지</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>보고서</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>실패</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>개 검사</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>{lib} 기반</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>구독</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>닫기</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>이메일 주소</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>you@example.com</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(선택)</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>취소</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>구독</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>닫기</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>개인정보 처리방침</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>오류:</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>XML로 변환</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>ICC로 변환</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>XML로 변환 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>프로파일 ID</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>태그 이름</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>오프셋</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>크기</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>패딩</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>유형</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>{type} 배열</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(내용 없음)</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>바이트</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>검증 출력 없음</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>심각한 검증 오류</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>유효</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>경고</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>오류</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>알 수 없음</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>통과</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>실패</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>검증 세부 정보</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>트리거 항목</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>항목</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>현재 값</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>필수: 0</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>예상: {value}</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>잘못됨</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>닫기</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>들여쓰기</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>키 정렬</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>목표 헤드룸</v>
+        <v>선형 값</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
+        <v>파일 1.0 = HDR 기준 흰색</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>톤 매핑</v>
+        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>OpenEXR 및 Radiance HDR 파일은 관례적으로 SDR 흰색을 1.0에 두지만, ICC 선형 전달 함수는 1.0을 1 cd/m²로 읽습니다. 기본값은 파일의 1.0이 프로파일의 HDR 기준 흰색에 오도록 크기를 조정합니다.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>게인 곡선 (HAGC)</v>
+        <v>입력 배율</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>미리 계산된 SDR 대체 (AToB0)</v>
+        <v>×{w} — 파일 1.0 = 기준 흰색</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>끄기 — 개정 이전 CMM과 동일</v>
+        <v>없음 — 파일 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>프로파일 적용 중…</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>HDR 프로파일</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>선형 전달 함수</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>비선형 전달 함수 (PQ, HLG)</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>기준선</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>색상 엔진을 통한 미리보기</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>{h}스톱에 맞춘 톤 매핑</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>기준 흰색</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>디스플레이 피크</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>미리보기를 사용할 수 없음: {why}</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
+        <v>색상 엔진을 통한 미리보기</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>모든 헤드룸에서의 게인</v>
+        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
+        <v>{h}스톱에 맞춘 톤 매핑</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>입력(HDR 기준 흰색 대비 스톱)</v>
+        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>디스플레이 헤드룸(스톱)</v>
+        <v>기준 흰색</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>게인(스톱)</v>
+        <v>디스플레이 피크</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>태그의 곡선</v>
+        <v>미리보기를 사용할 수 없음: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>기준선</v>
+        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>슬라이더</v>
+        <v>모든 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>입력 = 디스플레이 피크</v>
+        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>헤드룸별 회색 톤 곡선</v>
+        <v>입력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
+        <v>디스플레이 헤드룸(스톱)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>출력(HDR 기준 흰색 대비 스톱)</v>
+        <v>게인(스톱)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h}스톱</v>
+        <v>태그의 곡선</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h}스톱(기준선)</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>{h}스톱(슬라이더)</v>
+        <v>슬라이더</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>입력 = 디스플레이 피크</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>헤드룸별 회색 톤 곡선</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>출력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>{h}스톱</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>{h}스톱(기준선)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>{h}스톱(슬라이더)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>변경 없음</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>디스플레이 식별</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>색 원색</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>전달 특성</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>행렬 계수</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>풀 레인지</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>내로 레인지</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>보고서</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>실패</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>개 검사</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>{lib} 기반</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>구독</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>닫기</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>이메일 주소</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>you@example.com</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(선택)</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>취소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>구독</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>닫기</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>개인정보 처리방침</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>오류:</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>XML로 변환</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>JSON으로 변환</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>ICC로 변환</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>XML로 변환 중…</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>프로파일 ID</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>태그 이름</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>오프셋</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>크기</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>패딩</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>유형</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>{type} 배열</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(내용 없음)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>바이트</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>검증 출력 없음</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>심각한 검증 오류</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>유효</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>경고</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>알 수 없음</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>통과</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>실패</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>검증 세부 정보</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>트리거 항목</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>항목</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>현재 값</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>필수: 0</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>예상: {value}</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>잘못됨</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>닫기</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>들여쓰기</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>키 정렬</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>디코딩 중…</v>
+        <v>이 파일은 {size} MB입니다. HDR 탭은 {max} MB까지의 이미지만 엽니다.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>다이내믹 레인지</v>
+        <v>프로파일을 적용할 수 없음:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
+        <v>이미지를 그릴 수 없음:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
+        <v>(이 원색들은 색 공간을 정의하지 않음 — 무시하고 Rec. 709 사용)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>이 브라우저는 디코딩합니다</v>
+        <v>JPEG XL의 프로파일은 코드스트림 안에 압축되어 있으며, profiletool은 아직 이를 해제하지 못합니다</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>이 브라우저는 디코딩하지 않습니다</v>
+        <v>디코딩 중…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
+        <v>다이내믹 레인지</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
+        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>이후 릴리스로 연기됨</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
+        <v>이 브라우저는 디코딩합니다</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
+        <v>이 브라우저는 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
+        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
+        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
+        <v>이후 릴리스로 연기됨</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>알 수 없는 형식</v>
+        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{os}의 {browser}</v>
+        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · HDR 디스플레이 감지됨</v>
+        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · SDR 디스플레이</v>
+        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
+        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
+        <v>알 수 없는 형식</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>디스플레이 최대치</v>
+        <v>{os}의 {browser}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
+        <v>{name} · HDR 디스플레이 감지됨</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — SDR 디스플레이</v>
+        <v>{name} · SDR 디스플레이</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>알 수 없음</v>
+        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
+        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
+        <v>디스플레이 최대치</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
+        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>디스플레이에 맞춤</v>
+        <v>1× — SDR 디스플레이</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>이미지 세부 정보</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>사용할 수 없음 — 브라우저가 이 이미지를 렌더링하므로 지정한 피크로 제한할 수 없습니다</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>사용할 수 없음 — 이 출력은 SDR 흰색보다 밝은 부분을 표시하지 못합니다</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>사용할 수 없음 — 이 디스플레이의 피크를 알 수 없습니다</v>
+        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>확대</v>
+        <v>디스플레이에 맞춤</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>축소</v>
+        <v>이미지 세부 정보</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>이미지 맞춤</v>
+        <v>사용할 수 없음 — 브라우저가 이 이미지를 렌더링하므로 지정한 피크로 제한할 수 없습니다</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>실제 픽셀(1:1)</v>
+        <v>사용할 수 없음 — 이 출력은 SDR 흰색보다 밝은 부분을 표시하지 못합니다</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>드래그하여 이동 · Ctrl+휠로 확대/축소 · 더블클릭으로 초기화</v>
+        <v>사용할 수 없음 — 이 디스플레이의 피크를 알 수 없습니다</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>드래그하여 이미지 영역 크기 조정, 더블클릭하면 기본 크기로 돌아갑니다</v>
+        <v>확대</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>이미지 보기</v>
+        <v>축소</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
+        <v>이미지 맞춤</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>제한 없음</v>
+        <v>실제 픽셀(1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>제한 {n} 스톱 ({r}×)</v>
+        <v>드래그하여 이동 · Ctrl+휠로 확대/축소 · 더블클릭으로 초기화</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>SDR 흰색</v>
+        <v>드래그하여 이미지 영역 크기 조정, 더블클릭하면 기본 크기로 돌아갑니다</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
+        <v>이미지 보기</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>SDR 흰색 패치</v>
+        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
+        <v>제한 없음</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>프로파일 지정</v>
+        <v>제한 {n} 스톱 ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>없음 — 파일이 나타내는 대로</v>
+        <v>SDR 흰색</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>내장 프로파일 ({n} B)</v>
+        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>풀의 HDR 프로파일</v>
+        <v>SDR 흰색 패치</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>프로파일</v>
+        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>내장 프로파일</v>
+        <v>프로파일 지정</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>색상 엔진 경로</v>
+        <v>없음 — 파일이 나타내는 대로</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>HDR 경로, 게인 곡선 적용</v>
+        <v>내장 프로파일 ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR 경로, 게인 곡선 없음</v>
+        <v>풀의 HDR 프로파일</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>전달 함수</v>
+        <v>내장 프로파일</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR 기준 흰색</v>
+        <v>색상 엔진 경로</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>선형 값</v>
+        <v>HDR 경로, 게인 곡선 적용</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>파일 1.0 = HDR 기준 흰색</v>
+        <v>HDR 경로, 게인 곡선 없음</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
+        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>OpenEXR 및 Radiance HDR 파일은 관례적으로 SDR 흰색을 1.0에 두지만, ICC 선형 전달 함수는 1.0을 1 cd/m²로 읽습니다. 기본값은 파일의 1.0이 프로파일의 HDR 기준 흰색에 오도록 크기를 조정합니다.</v>
+        <v>전달 함수</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>입력 배율</v>
+        <v>HDR 기준 흰색</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — 파일 1.0 = 기준 흰색</v>
+        <v>선형 값</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>없음 — 파일 1.0 = 1 cd/m²</v>
+        <v>파일 1.0 = HDR 기준 흰색</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>목표 헤드룸</v>
+        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
+        <v>OpenEXR 및 Radiance HDR 파일은 관례적으로 SDR 흰색을 1.0에 두지만, ICC 선형 전달 함수는 1.0을 1 cd/m²로 읽습니다. 기본값은 파일의 1.0이 프로파일의 HDR 기준 흰색에 오도록 크기를 조정합니다.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>톤 매핑</v>
+        <v>입력 배율</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>×{w} — 파일 1.0 = 기준 흰색</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>게인 곡선 (HAGC)</v>
+        <v>없음 — 파일 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>미리 계산된 SDR 대체 (AToB0)</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>끄기 — 개정 이전 CMM과 동일</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>프로파일 적용 중…</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>HDR 프로파일</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>선형 전달 함수</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>비선형 전달 함수 (PQ, HLG)</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>기준선</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>색상 엔진을 통한 미리보기</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>{h}스톱에 맞춘 톤 매핑</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>기준 흰색</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>디스플레이 피크</v>
+        <v>색상 엔진을 통한 미리보기</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>미리보기를 사용할 수 없음: {why}</v>
+        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
+        <v>{h}스톱에 맞춘 톤 매핑</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>모든 헤드룸에서의 게인</v>
+        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
+        <v>기준 흰색</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>입력(HDR 기준 흰색 대비 스톱)</v>
+        <v>디스플레이 피크</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>디스플레이 헤드룸(스톱)</v>
+        <v>미리보기를 사용할 수 없음: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>게인(스톱)</v>
+        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>태그의 곡선</v>
+        <v>모든 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>기준선</v>
+        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>슬라이더</v>
+        <v>입력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>입력 = 디스플레이 피크</v>
+        <v>디스플레이 헤드룸(스톱)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>헤드룸별 회색 톤 곡선</v>
+        <v>게인(스톱)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
+        <v>태그의 곡선</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>출력(HDR 기준 흰색 대비 스톱)</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h}스톱</v>
+        <v>슬라이더</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h}스톱(기준선)</v>
+        <v>입력 = 디스플레이 피크</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>{h}스톱(슬라이더)</v>
+        <v>헤드룸별 회색 톤 곡선</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>출력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>{h}스톱</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>{h}스톱(기준선)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>{h}스톱(슬라이더)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>변경 없음</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>디스플레이 식별</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>색 원색</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>전달 특성</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>행렬 계수</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>풀 레인지</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>내로 레인지</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>보고서</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>실패</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>개 검사</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>{lib} 기반</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>구독</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>닫기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>이메일 주소</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>you@example.com</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(선택)</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>취소</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>구독</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>닫기</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>개인정보 처리방침</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>오류:</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>XML로 변환</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>JSON으로 변환</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>ICC로 변환</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>XML로 변환 중…</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>프로파일 ID</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>태그 이름</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>오프셋</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>크기</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>패딩</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>유형</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>{type} 배열</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(내용 없음)</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>바이트</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>검증 출력 없음</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>심각한 검증 오류</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>유효</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>경고</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>오류</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>알 수 없음</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>통과</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>실패</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>검증 세부 정보</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>트리거 항목</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>항목</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>현재 값</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>필수: 0</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>예상: {value}</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>잘못됨</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>닫기</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>들여쓰기</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>키 정렬</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC도.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC와 JPEG XL도.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되어 열리며, ‘ICC 프로파일 저장’을 클릭하기 전에는 다운로드되지 않습니다.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>이름순 정렬</v>
+        <v>탭하여 선택한 다음 탭을 눌러 보냅니다.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>.cube에서 새 프로파일</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되어 열리며, ‘ICC 프로파일 저장’을 클릭하기 전에는 다운로드되지 않습니다.</v>
+        <v>.cube에서 새 프로파일</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube 파일 선택</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되어 열리며, ‘ICC 프로파일 저장’을 클릭하기 전에는 다운로드되지 않습니다.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube 파일 선택</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>취소</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>만드는 중…</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>프로파일</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>비교</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>링크</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>스펙트럴</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>제거</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>색역 비교</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>렌더링 의도</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>셸</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>와이어프레임</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>축 번호</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>불투명도</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>색상</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>단색</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>값 기준</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>회전</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>턴테이블</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>궤도</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>드래그 속도</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>롤</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>롤 속도</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>색역 생성 중…</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>색역 없음</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>표시/숨기기</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 색역 셸</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>평면</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>링크</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>프로파일 이름</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>만들기</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>만드는 중…</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>링크 파이프라인</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>완료</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>이미지 확인 중…</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>이미지 변환</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>변환 중…</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>제거됨</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>앞으로 이동</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>뒤로 이동</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>위로 이동</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>아래로 이동</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>렌더링 인텐트 (전체)</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>이 변환의 렌더링 인텐트</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>변환마다 렌더링 인텐트가 다릅니다</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>체인</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>체인을 분석할 수 없습니다.</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>체인 확인 중…</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>체인이 연결되지 않습니다 ({detail}).</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>지우기</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink 이름</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>생성 중…</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>이미지를 처리하려면 체인을 구성하세요</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>변환된 이미지를 저장했습니다.</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>데이터 파일이 너무 큽니다.</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>데이터 변환</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>변환 중…</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>선호</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>관측자</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>광원</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>조건</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>중복 {n}건 필터링</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>중앙값</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>평균값</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>패치</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>중복 {n}건</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>변환 결과</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · 패치 {n}개</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>다른 이름으로 저장</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>저장</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>변환 반전</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>반전 중…</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>반전</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>마지막 단계</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>첫 단계</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>{in} 데이터 → {out} 검색</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE 비용</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>추출 후 체인에 추가</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>추출 중…</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>닫기</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>이미지 출력 옵션</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>인코딩</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>원본과 동일</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8비트</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16비트</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>부동소수점 (32비트)</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>압축</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>없음</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>플레이너</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>컴포지트</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>분리</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM 보간</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>사면체</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>선형</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICC 포함</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>스펙트럴 TIFF 조합</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>조합 후 저장</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>조합 중…</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n}개 채널을 조합했습니다.</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>취소</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>확인</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>파일 선택</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>헤더</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>태그</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>검증</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>분석</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>중립축 잉킹</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% 잉크</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 출력(톤)</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 출력(톤)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>극값 측색</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
+        <v>극값 측색</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
+        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>상대</v>
+        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>절대</v>
+        <v>상대</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>백색점</v>
+        <v>절대</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>흑색점</v>
+        <v>백색점</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>흑색점에서의 잉킹</v>
+        <v>흑색점</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>흑색점에서의 잉킹</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
+        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>솔리드 대 최대 크로마</v>
+        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>솔리드 대 최대 크로마</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>색상</v>
+        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>솔리드</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>최대 C*</v>
+        <v>솔리드</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>해당 잉킹</v>
+        <v>최대 C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>해당 잉킹</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>섀도 영역의 잉크 사용량</v>
+        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
+        <v>섀도 영역의 잉크 사용량</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>L* 고정 평면</v>
+        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>흑색점 보정 기준</v>
+        <v>L* 고정 평면</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>경로상 위치</v>
+        <v>흑색점 보정 기준</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>경로</v>
+        <v>경로상 위치</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>중성축을 지나는 원색 잉킹 경로</v>
+        <v>경로</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>색역 내의 세 경로 — 사이언→레드, 마젠타→그린, 옐로→블루 — 각각 양 끝점 명도의 중간에서 중성축을 지나 선택한 B2A 테이블을 통과합니다. 모든 샘플이 색역 안에 있으므로, 섀도 경로와 달리 착색제의 급격한 단차나 반전은 색역 매핑 아티팩트가 아니라 CLUT 평활도 결함입니다.</v>
+        <v>중성축을 지나는 원색 잉킹 경로</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>원색 잉킹 경로는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>색역 내의 세 경로 — 사이언→레드, 마젠타→그린, 옐로→블루 — 각각 양 끝점 명도의 중간에서 중성축을 지나 선택한 B2A 테이블을 통과합니다. 모든 샘플이 색역 안에 있으므로, 섀도 경로와 달리 착색제의 급격한 단차나 반전은 색역 매핑 아티팩트가 아니라 CLUT 평활도 결함입니다.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>경로상의 위치(중간이 중성)</v>
+        <v>원색 잉킹 경로는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>이 인텐트에 검은점 보정을 적용했습니다.</v>
+        <v>경로상의 위치(중간이 중성)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>잉크 사용량 통계</v>
+        <v>이 인텐트에 검은점 보정을 적용했습니다.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>프로파일이 각 착색제를 얼마나 사용하는지 합계와 전체 대비 비율로 표시 — 분판의 잉크 소비 특성입니다.</v>
+        <v>잉크 사용량 통계</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>잉크 사용량 통계는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>프로파일이 각 착색제를 얼마나 사용하는지 합계와 전체 대비 비율로 표시 — 분판의 잉크 소비 특성입니다.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>중성축</v>
+        <v>잉크 사용량 통계는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>평균 커버리지</v>
+        <v>중성축</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>잉크 비율</v>
+        <v>평균 커버리지</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>잉크 비율은 중성 구성의 지문입니다 — 각 착색제가 사용된 전체 잉크에서 차지하는 비율로, 샘플 수와 무관합니다.</v>
+        <v>잉크 비율</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>색역 내 점</v>
+        <v>잉크 비율은 중성 구성의 지문입니다 — 각 착색제가 사용된 전체 잉크에서 차지하는 비율로, 샘플 수와 무관합니다.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>색역 내 모든 색상에 대한 잉크 사용량은 B2A 방향 색역 경계가 필요하지만 아직 구축되지 않았습니다 — 대기 중.</v>
+        <v>색역 내 점</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>요약할 착색제 데이터가 없습니다.</v>
+        <v>색역 내 모든 색상에 대한 잉크 사용량은 B2A 방향 색역 경계가 필요하지만 아직 구축되지 않았습니다 — 대기 중.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>아래에서 B2A(PCS→장치) 테이블을 선택하면 각 착색제의 회색조 잉크 커버리지 이미지도 표시됩니다.</v>
+        <v>요약할 착색제 데이터가 없습니다.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>동일한 격자에서 각 착색제의 잉크 커버리지(어두울수록 잉크가 많음).</v>
+        <v>아래에서 B2A(PCS→장치) 테이블을 선택하면 각 착색제의 회색조 잉크 커버리지 이미지도 표시됩니다.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>시안</v>
+        <v>동일한 격자에서 각 착색제의 잉크 커버리지(어두울수록 잉크가 많음).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>마젠타</v>
+        <v>시안</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>옐로</v>
+        <v>마젠타</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>레드</v>
+        <v>옐로</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>그린</v>
+        <v>레드</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>블루</v>
+        <v>그린</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>블랙</v>
+        <v>블루</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>지각적</v>
+        <v>블랙</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>상대 색도</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>채도</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>절대 색도</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>프로파일 통계</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>왕복 ΔE</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>평균</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>최대</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>분석 중…</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>분석</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>플롯</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>원시 출력</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>곡선</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>입력 곡선</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>출력 곡선</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 이미지</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>색역 이미지</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>색도</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>산점도</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>톤 응답 곡선</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>곡선 표</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>표</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>데이터</v>
+        <v>표</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>평가</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>불러오는 중…</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>입력</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>출력</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>부동 소수점</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>격자점</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>정규화</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>사람용</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>장치 → PCS</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → 장치</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>불러오는 중…</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>적합성</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>품질</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>코드 포인트</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>게인 곡선</v>
+        <v>코드 포인트</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>환경</v>
+        <v>게인 곡선</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>SDR 폴백을 표시 중</v>
+        <v>환경</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>체인에 HDR 프로파일 포함</v>
+        <v>SDR 폴백을 표시 중</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR 프로파일을 통한 변환은 해당 AToB0Tag(8.10.6이 요구하는 고정 SDR 렌더링)를 사용합니다. 8.10.1이 TRC 태그를 허용하지 않기 때문입니다. 결과는 그 폴백이며 HDR 동작이 아닙니다.</v>
+        <v>체인에 HDR 프로파일 포함</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>이들은 TRC 태그가 없는 HDR 프로파일이므로 색영역은 AToB0Tag에서 구성됩니다. 이는 HDR 처리를 하지 않는 소비자를 위해 8.10.6 조항이 요구하는 고정된 SDR 렌더링입니다. 프로파일의 HDR 색영역이 아니며, 그것은 제한된 PCS에 그릴 수 없습니다.</v>
+        <v>HDR 프로파일을 통한 변환은 해당 AToB0Tag(8.10.6이 요구하는 고정 SDR 렌더링)를 사용합니다. 8.10.1이 TRC 태그를 허용하지 않기 때문입니다. 결과는 그 폴백이며 HDR 동작이 아닙니다.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>감지 중…</v>
+        <v>이들은 TRC 태그가 없는 HDR 프로파일이므로 색영역은 AToB0Tag에서 구성됩니다. 이는 HDR 처리를 하지 않는 소비자를 위해 8.10.6 조항이 요구하는 고정된 SDR 렌더링입니다. 프로파일의 HDR 색영역이 아니며, 그것은 제한된 PCS에 그릴 수 없습니다.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>환경을 감지할 수 없습니다.</v>
+        <v>감지 중…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>HDR 디스플레이</v>
+        <v>환경을 감지할 수 없습니다.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>광색역</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>HDR 캔버스 경로</v>
+        <v>광색역</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>HDR 캔버스 경로</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>없음</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>예</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>아니오</v>
+        <v>예</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>보고되지 않음</v>
+        <v>아니오</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>형식</v>
+        <v>보고되지 않음</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>검사</v>
+        <v>형식</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>표시</v>
+        <v>검사</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>포함된 ICC 프로파일 읽기 — 코덱 불필요</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>픽셀 표시</v>
+        <v>포함된 ICC 프로파일 읽기 — 코덱 불필요</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>흰색보다 밝게 렌더링</v>
+        <v>픽셀 표시</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>profiletool이 직접 디코딩하므로 브라우저와 무관</v>
+        <v>흰색보다 밝게 렌더링</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>이 브라우저는 디스플레이의 HDR 헤드룸을 보고하지 않았고 HDR 경로 존재 여부만 알 수 있습니다.</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>브라우저 플래그</v>
+        <v>이 브라우저는 디스플레이의 HDR 헤드룸을 보고하지 않았고 HDR 경로 존재 여부만 알 수 있습니다.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>켜짐</v>
+        <v>브라우저 플래그</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>꺼짐</v>
+        <v>켜짐</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>여기서는 감지할 수 없음</v>
+        <v>꺼짐</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>이 브라우저에서 HDR 렌더링에 필요합니다. WebGPU가 없어 HDR 캔버스가 유일한 경로입니다. 프로파일 검사는 이것 없이도 작동합니다.</v>
+        <v>여기서는 감지할 수 없음</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>선택 사항: HDR은 WebGPU로 렌더링할 수 있지만, 켜면 HDR 캔버스 경로가 추가되고 profiletool이 화면의 실제 HDR 헤드룸을 읽을 수 있습니다.</v>
+        <v>이 브라우저에서 HDR 렌더링에 필요합니다. WebGPU가 없어 HDR 캔버스가 유일한 경로입니다. 프로파일 검사는 이것 없이도 작동합니다.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>웹 페이지는 플래그 페이지를 열 수 없습니다. 이 주소를 주소창에 붙여넣고 Enabled로 설정한 뒤 브라우저를 다시 시작하세요.</v>
+        <v>선택 사항: HDR은 WebGPU로 렌더링할 수 있지만, 켜면 HDR 캔버스 경로가 추가되고 profiletool이 화면의 실제 HDR 헤드룸을 읽을 수 있습니다.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>복사</v>
+        <v>웹 페이지는 플래그 페이지를 열 수 없습니다. 이 주소를 주소창에 붙여넣고 Enabled로 설정한 뒤 브라우저를 다시 시작하세요.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>복사됨</v>
+        <v>복사</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>복사 실패 — 주소를 선택해 복사하세요.</v>
+        <v>복사됨</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>픽셀 비율</v>
+        <v>복사 실패 — 주소를 선택해 복사하세요.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>현재 모니터</v>
+        <v>픽셀 비율</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>이름 없음</v>
+        <v>현재 모니터</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>기본</v>
+        <v>이름 없음</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>내장</v>
+        <v>기본</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>HDR 헤드룸</v>
+        <v>내장</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>이 브라우저에서 제공하지 않음</v>
+        <v>HDR 헤드룸</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium은 이를 스톱 단위로 보고합니다: 디스플레이 최대 밝기 ÷ SDR 흰색 레벨의 log₂. Windows에서는 Chrome이 디스플레이를 다시 읽을 때(창을 다른 화면으로 옮기거나 Chrome을 다시 활성화할 때)만 갱신되며, 밝기를 바꿔도 갱신되지 않습니다.</v>
+        <v>이 브라우저에서 제공하지 않음</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} 스톱 (≈ SDR 흰색의 {ratio}배)</v>
+        <v>Chromium은 이를 스톱 단위로 보고합니다: 디스플레이 최대 밝기 ÷ SDR 흰색 레벨의 log₂. Windows에서는 Chrome이 디스플레이를 다시 읽을 때(창을 다른 화면으로 옮기거나 Chrome을 다시 활성화할 때)만 갱신되며, 밝기를 바꿔도 갱신되지 않습니다.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} 스톱 (≈ SDR 흰색의 {ratio}배)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>디스플레이 헤드룸에서의 게인</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>이 디스플레이에서 HDR 이미지 한 장을 봅니다. 브라우저가 디코딩할 수 있는 파일은 브라우저가 직접 표시하고, OpenEXR과 Radiance HDR은 profiletool이 디코딩해 렌더링합니다.</v>
+        <v>디스플레이 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>HDR 이미지를 여기에 놓거나 클릭해 선택하세요</v>
+        <v>이 디스플레이에서 HDR 이미지 한 장을 봅니다. 브라우저가 디코딩할 수 있는 파일은 브라우저가 직접 표시하고, OpenEXR과 Radiance HDR은 profiletool이 디코딩해 렌더링합니다.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC와 JPEG XL도.</v>
+        <v>HDR 이미지를 여기에 놓거나 클릭해 선택하세요</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>다른 이미지 선택</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG(게인 맵 JPEG 포함), PNG — Safari에서는 HEIC와 JPEG XL도.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>지우기</v>
+        <v>다른 이미지 선택</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>내장 ICC 프로파일</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>없음 — OpenEXR은 색도 좌표로 색을 나타냅니다</v>
+        <v>내장 ICC 프로파일</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>없음 — Radiance HDR은 PRIMARIES 헤더로 색을 나타냅니다</v>
+        <v>없음 — OpenEXR은 색도 좌표로 색을 나타냅니다</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>확인 중…</v>
+        <v>없음 — Radiance HDR은 PRIMARIES 헤더로 색을 나타냅니다</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>없음</v>
+        <v>확인 중…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>프로파일 탭에서 열기</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>게인 맵</v>
+        <v>프로파일 탭에서 열기</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>감지됨, 디코딩 안 함</v>
+        <v>게인 맵</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>이미지가 아닙니다. 프로파일은 프로파일 패널에서 불러오세요.</v>
+        <v>감지됨, 디코딩 안 함</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>profiletool이 인식하지 못하는 이미지 형식입니다.</v>
+        <v>이미지가 아닙니다. 프로파일은 프로파일 패널에서 불러오세요.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>TIFF 픽셀은 아직 여기에 표시되지 않습니다. 브라우저는 TIFF를 디코딩하지 않으며, 16비트 TIFF에서 HDR을 인코딩하는 방식도 아직 정해지지 않았습니다(4.3단계). 내장 프로파일은 검사할 수 있습니다.</v>
+        <v>profiletool이 인식하지 못하는 이미지 형식입니다.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>이 이미지는 여기서 표시할 수 없습니다:</v>
+        <v>TIFF 픽셀은 아직 여기에 표시되지 않습니다. 브라우저는 TIFF를 디코딩하지 않으며, 16비트 TIFF에서 HDR을 인코딩하는 방식도 아직 정해지지 않았습니다(4.3단계). 내장 프로파일은 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>내장 프로파일은 여전히 검사할 수 있습니다.</v>
+        <v>이 이미지는 여기서 표시할 수 없습니다:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>표시 주체</v>
+        <v>내장 프로파일은 여전히 검사할 수 있습니다.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>브라우저</v>
+        <v>표시 주체</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>브라우저</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>HDR 디스플레이</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>브라우저는 내장 ICC 프로파일로만 표시된 HDR을 무시하므로 이 이미지는 어둡고 밋밋해 보일 수 있습니다.</v>
+        <v>HDR 디스플레이</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>이 브라우저는 이미지를 SDR과 HDR 사이에서 전환할 수 없으므로 브라우저가 렌더링한 그대로 표시합니다.</v>
+        <v>브라우저는 내장 ICC 프로파일로만 표시된 HDR을 무시하므로 이 이미지는 어둡고 밋밋해 보일 수 있습니다.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>브라우저가 이 이미지를 디코딩하지 못했습니다.</v>
+        <v>이 브라우저는 이미지를 SDR과 HDR 사이에서 전환할 수 없으므로 브라우저가 렌더링한 그대로 표시합니다.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>출력</v>
+        <v>브라우저가 이 이미지를 디코딩하지 못했습니다.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>HDR 캔버스(float16)</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU(확장 범위)</v>
+        <v>HDR 캔버스(float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>SDR 캔버스(톤 매핑)</v>
+        <v>WebGPU(확장 범위)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>크기</v>
+        <v>SDR 캔버스(톤 매핑)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>가장 밝은 픽셀</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>SDR 흰색의 {n}배</v>
+        <v>가장 밝은 픽셀</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>색도 좌표</v>
+        <v>SDR 흰색의 {n}배</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>명시 안 됨 — Rec. 709로 가정</v>
+        <v>색도 좌표</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from}을(를) 여기서 사용할 수 없습니다({why}). 다음 출력을 사용합니다.</v>
+        <v>명시 안 됨 — Rec. 709로 가정</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>이 출력은 흰색보다 밝은 값을 담을 수 없어 톤 매핑된 SDR 렌더링을 표시합니다.</v>
+        <v>{from}을(를) 여기서 사용할 수 없습니다({why}). 다음 출력을 사용합니다.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>노출</v>
+        <v>이 출력은 흰색보다 밝은 값을 담을 수 없어 톤 매핑된 SDR 렌더링을 표시합니다.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} 스톱</v>
+        <v>노출</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>디코딩할 수 없음:</v>
+        <v>{n} 스톱</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>이 파일은 {size} MB입니다. HDR 탭은 {max} MB까지의 이미지만 엽니다.</v>
+        <v>디코딩할 수 없음:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>프로파일을 적용할 수 없음:</v>
+        <v>이 파일은 {size} MB입니다. HDR 탭은 {max} MB까지의 이미지만 엽니다.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>이미지를 그릴 수 없음:</v>
+        <v>프로파일을 적용할 수 없음:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(이 원색들은 색 공간을 정의하지 않음 — 무시하고 Rec. 709 사용)</v>
+        <v>이미지를 그릴 수 없음:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>JPEG XL의 프로파일은 코드스트림 안에 압축되어 있으며, profiletool은 아직 이를 해제하지 못합니다</v>
+        <v>(이 원색들은 색 공간을 정의하지 않음 — 무시하고 Rec. 709 사용)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>디코딩 중…</v>
+        <v>JPEG XL의 프로파일은 코드스트림 안에 압축되어 있으며, profiletool은 아직 이를 해제하지 못합니다</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>다이내믹 레인지</v>
+        <v>디코딩 중…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
+        <v>다이내믹 레인지</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
+        <v>이 브라우저는 양 끝만 제공하며 혼합은 지원하지 않습니다.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>이 브라우저는 디코딩합니다</v>
+        <v>profiletool이 직접 디코딩하므로 브라우저와 무관합니다</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>이 브라우저는 디코딩하지 않습니다</v>
+        <v>이 브라우저는 디코딩합니다</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
+        <v>이 브라우저는 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
+        <v>HEIC 표시에는 Safari 또는 다른 WebKit 브라우저가 필요합니다 — Chrome과 Firefox는 macOS를 포함한 어떤 플랫폼에서도 HEIC를 디코딩하지 않습니다</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>이후 릴리스로 연기됨</v>
+        <v>JPEG XL 표시에는 Safari가 필요합니다. 다른 브라우저는 아직 지원하지 않습니다</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
+        <v>이후 릴리스로 연기됨</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
+        <v>이 디스플레이는 HDR 경로를 보고하지 않아 HDR이 톤 매핑된 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
+        <v>이 브라우저에는 HDR 캔버스 경로가 없습니다(float16 캔버스 또는 WebGPU 필요)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
+        <v>Firefox는 HDR 이미지를 표시하지 않고 게인 맵도 읽지 않습니다. HDR 콘텐츠는 SDR로 표시됩니다</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
+        <v>검사에는 컨테이너 파싱만 필요하며 코덱은 필요 없습니다</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>알 수 없는 형식</v>
+        <v>HDR 디스플레이와 HDR 캔버스 경로를 모두 사용할 수 있습니다</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{os}의 {browser}</v>
+        <v>알 수 없는 형식</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · HDR 디스플레이 감지됨</v>
+        <v>{os}의 {browser}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · SDR 디스플레이</v>
+        <v>{name} · HDR 디스플레이 감지됨</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
+        <v>{name} · SDR 디스플레이</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
+        <v>WebGPU가 톤 매핑 “{mode}”을(를) 적용해 출력이 SDR로 제한됩니다</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>디스플레이 최대치</v>
+        <v>이 브라우저는 적용한 WebGPU 톤 매핑을 보고하지 않아 HDR 출력이 확인되지 않았습니다</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
+        <v>디스플레이 최대치</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — SDR 디스플레이</v>
+        <v>SDR 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>알 수 없음</v>
+        <v>1× — SDR 디스플레이</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 브라우저가 양 끝 모두에서 이 이미지를 SDR로 표시합니다.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
+        <v>이 디스플레이는 HDR을 보고하지 않아 SDR 흰색보다 밝은 부분은 잘립니다. “디스플레이에 맞춤”은 톤 매핑된 렌더링을 대신 표시합니다.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>디스플레이에 맞춤</v>
+        <v>이 이미지는 SDR 흰색의 {img}배를 요구하지만 이 디스플레이는 {disp}배까지만 표시하므로 더 밝은 값은 잘립니다. “디스플레이에 맞춤”은 이를 디스플레이 최대치까지 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>이미지 세부 정보</v>
+        <v>디스플레이에 맞춤</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>사용할 수 없음 — 브라우저가 이 이미지를 렌더링하므로 지정한 피크로 제한할 수 없습니다</v>
+        <v>이미지 세부 정보</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>사용할 수 없음 — 이 출력은 SDR 흰색보다 밝은 부분을 표시하지 못합니다</v>
+        <v>사용할 수 없음 — 브라우저가 이 이미지를 렌더링하므로 지정한 피크로 제한할 수 없습니다</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>사용할 수 없음 — 이 디스플레이의 피크를 알 수 없습니다</v>
+        <v>사용할 수 없음 — 이 출력은 SDR 흰색보다 밝은 부분을 표시하지 못합니다</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>확대</v>
+        <v>사용할 수 없음 — 이 디스플레이의 피크를 알 수 없습니다</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>축소</v>
+        <v>확대</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>이미지 맞춤</v>
+        <v>축소</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>실제 픽셀(1:1)</v>
+        <v>이미지 맞춤</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>드래그하여 이동 · Ctrl+휠로 확대/축소 · 더블클릭으로 초기화</v>
+        <v>실제 픽셀(1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>드래그하여 이미지 영역 크기 조정, 더블클릭하면 기본 크기로 돌아갑니다</v>
+        <v>드래그하여 이동 · Ctrl+휠로 확대/축소 · 더블클릭으로 초기화</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>이미지 보기</v>
+        <v>드래그하여 이미지 영역 크기 조정, 더블클릭하면 기본 크기로 돌아갑니다</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
+        <v>이미지 보기</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>제한 없음</v>
+        <v>이 디스플레이가 보고하는 최대치로 밝기를 제한합니다. Windows에서는 이 값이 밝기 변경을 늦게 따라갈 수 있습니다.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>제한 {n} 스톱 ({r}×)</v>
+        <v>제한 없음</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>SDR 흰색</v>
+        <v>제한 {n} 스톱 ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
+        <v>SDR 흰색</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>SDR 흰색 패치</v>
+        <v>비교용 일반 SDR 흰색입니다. HDR 디스플레이에서는 HDR 하이라이트가 이보다 밝게 보입니다.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
+        <v>SDR 흰색 패치</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>프로파일 지정</v>
+        <v>드래그해 옮기고, 더블클릭하면 이미지 옆으로 되돌립니다.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>없음 — 파일이 나타내는 대로</v>
+        <v>프로파일 지정</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>내장 프로파일 ({n} B)</v>
+        <v>없음 — 파일이 나타내는 대로</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>풀의 HDR 프로파일</v>
+        <v>내장 프로파일 ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>프로파일</v>
+        <v>풀의 HDR 프로파일</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>내장 프로파일</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>색상 엔진 경로</v>
+        <v>내장 프로파일</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR 경로, 게인 곡선 적용</v>
+        <v>색상 엔진 경로</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>HDR 경로, 게인 곡선 없음</v>
+        <v>HDR 경로, 게인 곡선 적용</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
+        <v>HDR 경로, 게인 곡선 없음</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>전달 함수</v>
+        <v>미리 계산된 AToB0 — HDR 경로 아님</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR 기준 흰색</v>
+        <v>전달 함수</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>선형 값</v>
+        <v>HDR 기준 흰색</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>파일 1.0 = HDR 기준 흰색</v>
+        <v>선형 값</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
+        <v>파일 1.0 = HDR 기준 흰색</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>OpenEXR 및 Radiance HDR 파일은 관례적으로 SDR 흰색을 1.0에 두지만, ICC 선형 전달 함수는 1.0을 1 cd/m²로 읽습니다. 기본값은 파일의 1.0이 프로파일의 HDR 기준 흰색에 오도록 크기를 조정합니다.</v>
+        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>입력 배율</v>
+        <v>OpenEXR 및 Radiance HDR 파일은 관례적으로 SDR 흰색을 1.0에 두지만, ICC 선형 전달 함수는 1.0을 1 cd/m²로 읽습니다. 기본값은 파일의 1.0이 프로파일의 HDR 기준 흰색에 오도록 크기를 조정합니다.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — 파일 1.0 = 기준 흰색</v>
+        <v>입력 배율</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>없음 — 파일 1.0 = 1 cd/m²</v>
+        <v>×{w} — 파일 1.0 = 기준 흰색</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>목표 헤드룸</v>
+        <v>없음 — 파일 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
+        <v>목표 헤드룸</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>톤 매핑</v>
+        <v>기준 흰색의 {r}배 ({n} 스톱)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>톤 매핑</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>게인 곡선 (HAGC)</v>
+        <v>자동 (8.10.3항 우선순위)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>미리 계산된 SDR 대체 (AToB0)</v>
+        <v>게인 곡선 (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>끄기 — 개정 이전 CMM과 동일</v>
+        <v>미리 계산된 SDR 대체 (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>프로파일 적용 중…</v>
+        <v>끄기 — 개정 이전 CMM과 동일</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
+        <v>프로파일 적용 중…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 Linear (8)인 프로파일이 필요합니다.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
+        <v>프로파일을 지정하려면 3채널 RGB 이미지가 필요합니다.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>HDR 프로파일</v>
+        <v>값을 해석하려면 위에서 프로파일을 지정하세요.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>선형 전달 함수</v>
+        <v>HDR 프로파일</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>비선형 전달 함수 (PQ, HLG)</v>
+        <v>선형 전달 함수</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>비선형 전달 함수 (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>HDR 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>기준선</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>색상 엔진을 통한 미리보기</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
+        <v>색상 엔진을 통한 미리보기</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>{h}스톱에 맞춘 톤 매핑</v>
+        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
+        <v>{h}스톱에 맞춘 톤 매핑</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>기준 흰색</v>
+        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>디스플레이 피크</v>
+        <v>기준 흰색</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>미리보기를 사용할 수 없음: {why}</v>
+        <v>디스플레이 피크</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
+        <v>미리보기를 사용할 수 없음: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>모든 헤드룸에서의 게인</v>
+        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
+        <v>모든 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>입력(HDR 기준 흰색 대비 스톱)</v>
+        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>디스플레이 헤드룸(스톱)</v>
+        <v>입력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>게인(스톱)</v>
+        <v>디스플레이 헤드룸(스톱)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>태그의 곡선</v>
+        <v>게인(스톱)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>기준선</v>
+        <v>태그의 곡선</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>슬라이더</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>입력 = 디스플레이 피크</v>
+        <v>슬라이더</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>헤드룸별 회색 톤 곡선</v>
+        <v>입력 = 디스플레이 피크</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
+        <v>헤드룸별 회색 톤 곡선</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>출력(HDR 기준 흰색 대비 스톱)</v>
+        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h}스톱</v>
+        <v>출력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h}스톱(기준선)</v>
+        <v>{h}스톱</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>{h}스톱(슬라이더)</v>
+        <v>{h}스톱(기준선)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>{h}스톱(슬라이더)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>변경 없음</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>디스플레이 식별</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>색 원색</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>전달 특성</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>행렬 계수</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>풀 레인지</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>내로 레인지</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>보고서</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>이름순 정렬</v>
+        <v>탭하여 선택한 다음 탭을 눌러 보냅니다.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>.cube에서 새 프로파일</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되어 열리며, ‘ICC 프로파일 저장’을 클릭하기 전에는 다운로드되지 않습니다.</v>
+        <v>.cube에서 새 프로파일</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube 파일 선택</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되어 열리며, ‘ICC 프로파일 저장’을 클릭하기 전에는 다운로드되지 않습니다.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube 파일 선택</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>취소</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>만드는 중…</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>프로파일</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>비교</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>링크</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>스펙트럴</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>제거</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>색역 비교</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>렌더링 의도</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>셸</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>와이어프레임</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>축 번호</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>불투명도</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>색상</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>단색</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>값 기준</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>회전</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>턴테이블</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>궤도</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>드래그 속도</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>롤</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>롤 속도</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>색역 생성 중…</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>색역 없음</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>표시/숨기기</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 색역 셸</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>평면</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>링크</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>프로파일 이름</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>만들기</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>만드는 중…</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>링크 파이프라인</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>완료</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>이미지 확인 중…</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>이미지 변환</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>변환 중…</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>제거됨</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>앞으로 이동</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>뒤로 이동</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>위로 이동</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>아래로 이동</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>렌더링 인텐트 (전체)</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>이 변환의 렌더링 인텐트</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>변환마다 렌더링 인텐트가 다릅니다</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>체인</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>체인을 분석할 수 없습니다.</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>체인 확인 중…</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>체인이 연결되지 않습니다 ({detail}).</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>지우기</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink 이름</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>생성 중…</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>이미지를 처리하려면 체인을 구성하세요</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>변환된 이미지를 저장했습니다.</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>데이터 파일이 너무 큽니다.</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>데이터 변환</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>변환 중…</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>선호</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>관측자</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>광원</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>조건</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>중복 {n}건 필터링</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>중앙값</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>평균값</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>패치</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>중복 {n}건</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>변환 결과</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · 패치 {n}개</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>다른 이름으로 저장</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>저장</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>변환 반전</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>반전 중…</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>반전</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>마지막 단계</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>첫 단계</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>{in} 데이터 → {out} 검색</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE 비용</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>추출 후 체인에 추가</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>추출 중…</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>닫기</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>이미지 출력 옵션</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>인코딩</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>원본과 동일</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8비트</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16비트</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>부동소수점 (32비트)</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>압축</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>없음</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>플레이너</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>컴포지트</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>분리</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM 보간</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>사면체</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>선형</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICC 포함</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>스펙트럴 TIFF 조합</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>조합 후 저장</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>조합 중…</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n}개 채널을 조합했습니다.</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>취소</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>확인</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>파일 선택</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>헤더</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>태그</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>검증</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>분석</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>중립축 잉킹</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% 잉크</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 출력(톤)</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 출력(톤)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>극값 측색</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
+        <v>극값 측색</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
+        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>상대</v>
+        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>절대</v>
+        <v>상대</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>백색점</v>
+        <v>절대</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>흑색점</v>
+        <v>백색점</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>흑색점에서의 잉킹</v>
+        <v>흑색점</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>흑색점에서의 잉킹</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
+        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>솔리드 대 최대 크로마</v>
+        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>솔리드 대 최대 크로마</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>색상</v>
+        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>솔리드</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>최대 C*</v>
+        <v>솔리드</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>해당 잉킹</v>
+        <v>최대 C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>해당 잉킹</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>섀도 영역의 잉크 사용량</v>
+        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
+        <v>섀도 영역의 잉크 사용량</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>L* 고정 평면</v>
+        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>흑색점 보정 기준</v>
+        <v>L* 고정 평면</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>경로상 위치</v>
+        <v>흑색점 보정 기준</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>경로</v>
+        <v>경로상 위치</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>중성축을 지나는 원색 잉킹 경로</v>
+        <v>경로</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>색역 내의 세 경로 — 사이언→레드, 마젠타→그린, 옐로→블루 — 각각 양 끝점 명도의 중간에서 중성축을 지나 선택한 B2A 테이블을 통과합니다. 모든 샘플이 색역 안에 있으므로, 섀도 경로와 달리 착색제의 급격한 단차나 반전은 색역 매핑 아티팩트가 아니라 CLUT 평활도 결함입니다.</v>
+        <v>중성축을 지나는 원색 잉킹 경로</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>원색 잉킹 경로는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>색역 내의 세 경로 — 사이언→레드, 마젠타→그린, 옐로→블루 — 각각 양 끝점 명도의 중간에서 중성축을 지나 선택한 B2A 테이블을 통과합니다. 모든 샘플이 색역 안에 있으므로, 섀도 경로와 달리 착색제의 급격한 단차나 반전은 색역 매핑 아티팩트가 아니라 CLUT 평활도 결함입니다.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>경로상의 위치(중간이 중성)</v>
+        <v>원색 잉킹 경로는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>이 인텐트에 검은점 보정을 적용했습니다.</v>
+        <v>경로상의 위치(중간이 중성)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>잉크 사용량 통계</v>
+        <v>이 인텐트에 검은점 보정을 적용했습니다.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>프로파일이 각 착색제를 얼마나 사용하는지 합계와 전체 대비 비율로 표시 — 분판의 잉크 소비 특성입니다.</v>
+        <v>잉크 사용량 통계</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>잉크 사용량 통계는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>프로파일이 각 착색제를 얼마나 사용하는지 합계와 전체 대비 비율로 표시 — 분판의 잉크 소비 특성입니다.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>중성축</v>
+        <v>잉크 사용량 통계는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>평균 커버리지</v>
+        <v>중성축</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>잉크 비율</v>
+        <v>평균 커버리지</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>잉크 비율은 중성 구성의 지문입니다 — 각 착색제가 사용된 전체 잉크에서 차지하는 비율로, 샘플 수와 무관합니다.</v>
+        <v>잉크 비율</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>색역 내 점</v>
+        <v>잉크 비율은 중성 구성의 지문입니다 — 각 착색제가 사용된 전체 잉크에서 차지하는 비율로, 샘플 수와 무관합니다.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>색역 내 모든 색상에 대한 잉크 사용량은 B2A 방향 색역 경계가 필요하지만 아직 구축되지 않았습니다 — 대기 중.</v>
+        <v>색역 내 점</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>요약할 착색제 데이터가 없습니다.</v>
+        <v>색역 내 모든 색상에 대한 잉크 사용량은 B2A 방향 색역 경계가 필요하지만 아직 구축되지 않았습니다 — 대기 중.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>아래에서 B2A(PCS→장치) 테이블을 선택하면 각 착색제의 회색조 잉크 커버리지 이미지도 표시됩니다.</v>
+        <v>요약할 착색제 데이터가 없습니다.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>동일한 격자에서 각 착색제의 잉크 커버리지(어두울수록 잉크가 많음).</v>
+        <v>아래에서 B2A(PCS→장치) 테이블을 선택하면 각 착색제의 회색조 잉크 커버리지 이미지도 표시됩니다.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>시안</v>
+        <v>동일한 격자에서 각 착색제의 잉크 커버리지(어두울수록 잉크가 많음).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>마젠타</v>
+        <v>시안</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>옐로</v>
+        <v>마젠타</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>레드</v>
+        <v>옐로</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>그린</v>
+        <v>레드</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>블루</v>
+        <v>그린</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>블랙</v>
+        <v>블루</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>지각적</v>
+        <v>블랙</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>상대 색도</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>채도</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>절대 색도</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>프로파일 통계</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>왕복 ΔE</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>평균</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>최대</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>분석 중…</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>분석</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>플롯</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>원시 출력</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>곡선</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>입력 곡선</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>출력 곡선</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 이미지</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>색역 이미지</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>색도</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>산점도</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>톤 응답 곡선</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>곡선 표</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>표</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>데이터</v>
+        <v>표</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>평가</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>불러오는 중…</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>입력</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>출력</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>부동 소수점</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>격자점</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>정규화</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>사람용</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>장치 → PCS</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → 장치</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>불러오는 중…</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>적합성</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>품질</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>보고서</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>체인에 HDR 프로파일 포함</v>
+        <v>체인에 HDR ColorSpace 프로파일 포함</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>HDR 프로파일을 통한 변환은 해당 AToB0Tag(8.10.6이 요구하는 고정 SDR 렌더링)를 사용합니다. 8.10.1이 TRC 태그를 허용하지 않기 때문입니다. 결과는 그 폴백이며 HDR 동작이 아닙니다.</v>
+        <v>HDR 프로파일을 통한 변환은 해당 AToB0Tag(8.7.1.5이 요구하는 고정 SDR 렌더링)를 사용합니다. ColorSpace 프로파일에는 TRC 태그가 없기 때문입니다. 결과는 그 폴백이며 HDR 동작이 아닙니다.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>이들은 TRC 태그가 없는 HDR 프로파일이므로 색영역은 AToB0Tag에서 구성됩니다. 이는 HDR 처리를 하지 않는 소비자를 위해 8.10.6 조항이 요구하는 고정된 SDR 렌더링입니다. 프로파일의 HDR 색영역이 아니며, 그것은 제한된 PCS에 그릴 수 없습니다.</v>
+        <v>이들은 TRC 태그가 없는 HDR 프로파일이므로 색영역은 AToB0Tag에서 구성됩니다. 이는 HDR 처리를 하지 않는 소비자를 위해 8.7.1.5 조항이 요구하는 고정된 SDR 렌더링입니다. 프로파일의 HDR 색영역이 아니며, 그것은 제한된 PCS에 그릴 수 없습니다.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.10.2 a)</v>
+        <v>파일 1.0 = 1 cd/m²(ICC.1 조항 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>자동 (8.10.3항 우선순위)</v>
+        <v>자동 (8.7.1.3항 우선순위)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>HDR 프로파일</v>
+        <v>HDR ColorSpace 프로파일</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR 프로파일 — 선형 전달 함수</v>
+        <v>HDR ColorSpace 프로파일 — 선형 전달 함수</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>HDR 프로파일 — PQ / HLG 전달 함수</v>
+        <v>HDR ColorSpace 프로파일 — PQ / HLG 전달 함수</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR 프로파일만 지정할 수 있습니다.</v>
+        <v>{format}은 선형 광을 담으므로 전달 함수가 선형인 HDR ColorSpace 프로파일만 지정할 수 있습니다.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>풀의 PQ/HLG HDR 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
+        <v>풀의 PQ/HLG HDR ColorSpace 프로파일 {n}개는 선택지에 없습니다 — 프로파일 패널의 HDR ColorSpace 프로파일 › 비선형 전달 함수 아래에 있습니다.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>풀에 아직 선형 전달 함수 HDR 프로파일이 없습니다. 프로파일 패널은 HDR 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
+        <v>풀에 아직 선형 전달 함수 HDR ColorSpace 프로파일이 없습니다. 프로파일 패널은 HDR ColorSpace 프로파일을 전달 함수별로 묶어 보여 줍니다.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.10.3항).</v>
+        <v>원색 미지정: 이 빌드에서는 HDR 경로 없음</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>디스플레이 헤드룸</v>
+        <v>IccProfLib이 이 게인 곡선의 적용을 거부했습니다: {why}. CMM은 다음 톤 매핑 기술자로 넘어갑니다(8.7.1.3항).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
+        <v>디스플레이 헤드룸</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>기준선</v>
+        <v>{n} 스톱 (≈ 기준 흰색의 {r}배)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>색상 엔진을 통한 미리보기</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
+        <v>색상 엔진을 통한 미리보기</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>{h}스톱에 맞춘 톤 매핑</v>
+        <v>작성된 그대로(기준선 {h}스톱, 게인 없음)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
+        <v>{h}스톱에 맞춘 톤 매핑</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>기준 흰색</v>
+        <v>동일한 테스트 픽셀({transfer} 신호가 왼쪽에서 오른쪽으로 증가: 회색, 이어서 R, G, B, Y, C, M)을 IccProfLib의 HDR 변환에 통과시킨 결과입니다. 두 띠 모두 HDR 기준 흰색의 {r}배로 제한되어, 헤드룸이 {h}스톱인 디스플레이에서 보이는 모습입니다. 위쪽 띠가 평평하게 잘리는 곳에서 게인 곡선이 하이라이트를 부드럽게 줄입니다.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>디스플레이 피크</v>
+        <v>기준 흰색</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>미리보기를 사용할 수 없음: {why}</v>
+        <v>디스플레이 피크</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
+        <v>미리보기를 사용할 수 없음: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>모든 헤드룸에서의 게인</v>
+        <v>색상 엔진이 이 프로파일에 HDR 경로를 사용하지 않았습니다</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
+        <v>모든 헤드룸에서의 게인</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>입력(HDR 기준 흰색 대비 스톱)</v>
+        <v>각 디스플레이 헤드룸에서 회색 입력에 적용되는 게인: 파란색은 압축, 빨간색은 확장, 흰색은 변화 없음입니다. 점선은 태그의 곡선, 실선은 기준선, 호박색 선은 슬라이더이며, 파선 대각선은 입력이 디스플레이 피크에 도달하는 위치입니다. 클릭하면 슬라이더가 이동합니다.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>디스플레이 헤드룸(스톱)</v>
+        <v>입력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>게인(스톱)</v>
+        <v>디스플레이 헤드룸(스톱)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>태그의 곡선</v>
+        <v>게인(스톱)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>기준선</v>
+        <v>태그의 곡선</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>슬라이더</v>
+        <v>기준선</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>입력 = 디스플레이 피크</v>
+        <v>슬라이더</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>헤드룸별 회색 톤 곡선</v>
+        <v>입력 = 디스플레이 피크</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
+        <v>헤드룸별 회색 톤 곡선</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>출력(HDR 기준 흰색 대비 스톱)</v>
+        <v>태그에 저장된 각 헤드룸에서의 회색 톤 곡선을 낮음(파랑)에서 높음(빨강)으로 색칠하고, 슬라이더 곡선은 호박색으로 표시합니다. 두 축 모두 스톱 단위이므로 대각선은 변화 없음을 뜻합니다.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h}스톱</v>
+        <v>출력(HDR 기준 흰색 대비 스톱)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h}스톱(기준선)</v>
+        <v>{h}스톱</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>{h}스톱(슬라이더)</v>
+        <v>{h}스톱(기준선)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
+        <v>{h}스톱(슬라이더)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
+        <v>태그의 곡선(헤드룸 순): {list} 스톱. 기준선 {b} 스톱, HDR 기준 흰색 {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
+        <v>이 헤드룸은 태그 곡선의 범위를 벗어나므로 가장 가까운 곡선을 그대로 사용합니다 — 라이브러리는 범위 밖으로 외삽하지 않습니다.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
+        <v>일부 기울기는 태그에 저장되지 않고 도출되었습니다(PCHIP). 이 도출은 SMPTE 조항을 재구성한 것이므로 해당 곡선의 모양은 잠정적인 것으로 보세요.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
+        <v>이 태그는 기준 흰색 톤 매핑을 요청하므로 곡선을 파일에서 읽지 않고 라이브러리가 구성합니다(위원회 초안의 구성).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
+        <v>대체 이미지 없음: 이 태그는 톤 매핑을 요청하지 않고 디스플레이 색 볼륨으로의 클램프만 요청합니다.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 스톱 곡선(게인 없음)</v>
+        <v>이 헤드룸에서 혼합되는 두 곡선은 색 채널을 서로 다르게 혼합하므로 하나의 게인 곡선으로 그릴 수 없습니다. 아래 톤 곡선은 여전히 정확합니다.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>{h} 스톱 곡선</v>
+        <v>{h} 스톱 곡선(게인 없음)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>{h} 스톱에서 적용</v>
+        <v>{h} 스톱 곡선</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>이 헤드룸에서 적용되는 게인</v>
+        <v>{h} 스톱에서 적용</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
+        <v>이 헤드룸에서 적용되는 게인</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>게인(log2 스톱)</v>
+        <v>혼합 입력(선형, 1.0 = HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>이 헤드룸에서의 회색 톤 곡선</v>
+        <v>게인(log2 스톱)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>입력(× HDR 기준 흰색)</v>
+        <v>이 헤드룸에서의 회색 톤 곡선</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>출력(× HDR 기준 흰색)</v>
+        <v>입력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>변경 없음</v>
+        <v>출력(× HDR 기준 흰색)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 스톱에서의 디스플레이 최대치</v>
+        <v>변경 없음</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>{h} 스톱에서의 출력</v>
+        <v>{h} 스톱에서의 디스플레이 최대치</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
+        <v>{h} 스톱에서의 출력</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>디스플레이 식별</v>
+        <v>HDR, 색역, 픽셀 비율은 이 값이 다른 화면으로 창을 옮기면 갱신됩니다.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
+        <v>디스플레이 식별</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>이 창이 있는 모니터를 추적 중입니다.</v>
+        <v>이 창이 어느 모니터에 있는지 알기 위한 권한을 요청합니다. 비슷한 화면 사이에서도 갱신되고, 브라우저가 제공하면 HDR 헤드룸도 표시합니다.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
+        <v>이 창이 있는 모니터를 추적 중입니다.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
+        <v>디스플레이 식별 권한이 거부되었습니다. 이 사이트의 설정에서 변경할 수 있습니다.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>디스플레이를 식별할 수 없습니다.</v>
+        <v>이 브라우저는 디스플레이를 식별할 수 없습니다. 위의 자동 갱신만 적용됩니다.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>디스플레이 이벤트</v>
+        <v>디스플레이를 식별할 수 없습니다.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
+        <v>디스플레이 이벤트</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>색 원색</v>
+        <v>아직 이벤트가 없습니다. 창을 다른 모니터로 끌어 보세요.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>전달 특성</v>
+        <v>색 원색</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>행렬 계수</v>
+        <v>전달 특성</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>비디오 풀 레인지 플래그</v>
+        <v>행렬 계수</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>풀 레인지</v>
+        <v>비디오 풀 레인지 플래그</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>내로 레인지</v>
+        <v>풀 레인지</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>ITU-T H.273에서 할당되지 않음</v>
+        <v>내로 레인지</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
+        <v>ITU-T H.273에서 할당되지 않음</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
+        <v>원색 2(지정되지 않음)는 원색을 프로파일 자체에 위임합니다. 원색은 이 태그가 아니라 착색제 태그에서 가져옵니다.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>보고서</v>
+        <v>이 태그의 예약된 4바이트가 모두 0은 아닙니다.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>